--- a/histograms/histogram_Combined_feature.xlsx
+++ b/histograms/histogram_Combined_feature.xlsx
@@ -442,79 +442,79 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>400000</v>
+        <v>1386.1125</v>
       </c>
       <c r="B2" t="n">
-        <v>26298</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1200000</v>
+        <v>4158.3375</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000000</v>
+        <v>6930.5625</v>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2800000</v>
+        <v>9702.787499999999</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3600000</v>
+        <v>12475.0125</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4400000</v>
+        <v>15247.2375</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5200000</v>
+        <v>18019.4625</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6000000</v>
+        <v>20791.6875</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6800000</v>
+        <v>23563.9125</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7600000</v>
+        <v>26336.1375</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8400000</v>
+        <v>29108.3625</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9200000</v>
+        <v>31880.5875</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -538,15 +538,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10000000</v>
+        <v>34652.8125</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10800000</v>
+        <v>37425.0375</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -554,15 +554,15 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11600000</v>
+        <v>40197.2625</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12400000</v>
+        <v>42969.4875</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13200000</v>
+        <v>45741.71249999999</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14000000</v>
+        <v>48513.9375</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14800000</v>
+        <v>51286.1625</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15600000</v>
+        <v>54058.3875</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
